--- a/kappa.xlsx
+++ b/kappa.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27809"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uoc0-my.sharepoint.com/personal/egortega_uoc_edu/Documents/UOC/PhD_Ortega_E/systematic_literature_review_artificial_agents_emotion_regulation/automated_app_reviews/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{8CBF9EA9-A1B8-45C9-B23A-9EB7495DE93D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB0D5CA4-F758-4807-98EB-3172BD486F7E}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="13_ncr:1_{8CBF9EA9-A1B8-45C9-B23A-9EB7495DE93D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27FB9663-17C9-44B9-97ED-B18A50CA0149}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4518B3E3-3D5F-4CFF-BA60-B98C1C335614}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="19">
   <si>
     <t>Cohen's Kappa</t>
   </si>
@@ -50,9 +50,15 @@
     <t>SSRI</t>
   </si>
   <si>
+    <t>Moderate Agreement</t>
+  </si>
+  <si>
     <t>IVM</t>
   </si>
   <si>
+    <t>Substantial Agreement</t>
+  </si>
+  <si>
     <t>LPVR</t>
   </si>
   <si>
@@ -62,22 +68,22 @@
     <t>Near Perfect Agreement</t>
   </si>
   <si>
-    <t>Moderate Agreement</t>
-  </si>
-  <si>
-    <t>Substantial Agreement</t>
+    <t>Human 1 - Automatic Screener</t>
+  </si>
+  <si>
+    <t>Human 2 - Automatic Screener (30%)</t>
+  </si>
+  <si>
+    <t>Excluded</t>
+  </si>
+  <si>
+    <t>Included</t>
   </si>
   <si>
     <t>Totals</t>
   </si>
   <si>
     <t>Observed Agreement</t>
-  </si>
-  <si>
-    <t>Excluded</t>
-  </si>
-  <si>
-    <t>Included</t>
   </si>
   <si>
     <t>Expected Agreement</t>
@@ -93,7 +99,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -152,9 +158,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -192,7 +198,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -298,7 +304,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -440,7 +446,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -448,19 +454,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{660D2E13-A122-426F-B47F-66558A972E9E}">
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -471,7 +477,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -479,43 +485,51 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2">
         <v>0.72</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>0.51</v>
       </c>
       <c r="C5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>6</v>
       </c>
       <c r="B6">
         <v>0.91</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15">
       <c r="B8" t="s">
         <v>12</v>
       </c>
@@ -523,10 +537,19 @@
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="H8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -540,8 +563,21 @@
         <f>SUM(B9:C9)</f>
         <v>1328</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9">
+        <v>386</v>
+      </c>
+      <c r="I9">
+        <v>15</v>
+      </c>
+      <c r="J9">
+        <f>SUM(H9:I9)</f>
+        <v>401</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -555,10 +591,23 @@
         <f>SUM(B10:C10)</f>
         <v>48</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10">
+        <v>4</v>
+      </c>
+      <c r="I10">
+        <v>8</v>
+      </c>
+      <c r="J10">
+        <f>SUM(H10:I10)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B11">
         <f>SUM(B9:B10)</f>
@@ -572,40 +621,79 @@
         <f>SUM(B9:C10)</f>
         <v>1376</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11">
+        <f>SUM(H9:H10)</f>
+        <v>390</v>
+      </c>
+      <c r="I11">
+        <f>SUM(I9:I10)</f>
+        <v>23</v>
+      </c>
+      <c r="J11">
+        <f>SUM(H9:I10)</f>
+        <v>413</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B12">
         <f>(B9+C10)/D11</f>
         <v>0.95348837209302328</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12">
+        <f>(H9+I10)/J11</f>
+        <v>0.95399515738498786</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B13">
         <f>((B9+C9)/D11) * ((B9+B10)/D11)+((B10+C10)/D11) * ((C9+C10)/D11)</f>
         <v>0.91373715521903742</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13">
+        <f>((H9+I9)/J11) * ((H9+H10)/J11)+((H10+I10)/J11) * ((I9+I10)/J11)</f>
+        <v>0.91849046426959169</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B14">
         <f>(B12-B13)/(1-B13)</f>
         <v>0.46081504702194326</v>
       </c>
       <c r="C14" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="G14" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14">
+        <f>(H12-H13)/(1-H13)</f>
+        <v>0.43558944112781434</v>
+      </c>
+      <c r="I14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15">
       <c r="B15" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
